--- a/docs/downloads/05/tbl_revtot_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_revtot_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2">
@@ -403,7 +403,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3">
@@ -422,7 +422,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B5">
@@ -460,7 +460,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B6">
@@ -479,7 +479,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B7">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B8">
@@ -517,7 +517,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B9">
@@ -536,7 +536,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B10">
